--- a/_999_SystemText.xlsx
+++ b/_999_SystemText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BF7697-4E58-4AE0-9C34-F215950BCBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2357D17B-CEC0-4205-9F63-E2005BFDB758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="4147" windowWidth="21600" windowHeight="11333" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="4763" yWindow="2798" windowWidth="21599" windowHeight="11332" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -205,6 +205,102 @@
   </si>
   <si>
     <t>まだ準備中です。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새로운 버전이 확인 되었습니다.
+업데이트 바랍니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A new version is available.
+Please update the application.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>新しいバ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ージョンが利用可能です。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+アプリをアップデ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ートしてください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업데이트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>アップデ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ート</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unable to check the latest version.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>最新バ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ージョンを確認できません。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최신 버전을 확인할 수 없습니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -809,33 +905,57 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+    <row r="11" spans="1:9" s="3" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A11" s="5">
+        <v>9990008</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="69.75" x14ac:dyDescent="0.6">
+      <c r="A12" s="4">
+        <v>9990009</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+    <row r="13" spans="1:9" s="3" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A13" s="5">
+        <v>9990010</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>

--- a/_999_SystemText.xlsx
+++ b/_999_SystemText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2357D17B-CEC0-4205-9F63-E2005BFDB758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D03651-0516-45CA-A5E4-B4B584995BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4763" yWindow="2798" windowWidth="21599" windowHeight="11332" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -301,6 +301,42 @@
   </si>
   <si>
     <t>최신 버전을 확인할 수 없습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Account</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Log Out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그아웃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>アカウント</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ログアウト</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그아웃 하시겠습니까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Would you like to log out?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ログアウトしますか？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -963,10 +999,18 @@
       <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="A14" s="4">
+        <v>9990011</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -974,10 +1018,18 @@
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="A15" s="5">
+        <v>9990012</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -985,10 +1037,18 @@
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="A16" s="4">
+        <v>9990013</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
